--- a/data/smurf.xlsx
+++ b/data/smurf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ueahome\eressci1\hpd08ucu\data\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ueanorwich-my.sharepoint.com/personal/hpd08ucu_uea_ac_uk/Documents/Manuscripts/cardinal_fitness/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA393328-45FD-4DC8-9A04-0FA2AA57CFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{AA393328-45FD-4DC8-9A04-0FA2AA57CFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81EFC0BD-9F2E-4EF8-BBCD-F62641EF3A04}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{1B2D4F02-B4A6-494B-BE29-BF10FB07563C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1B2D4F02-B4A6-494B-BE29-BF10FB07563C}"/>
   </bookViews>
   <sheets>
     <sheet name="Smurf survival after feeding" sheetId="2" r:id="rId1"/>
@@ -756,9 +756,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -796,7 +796,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -902,7 +902,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1044,7 +1044,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1055,6 +1055,8 @@
   <dimension ref="A1:P1837"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" customWidth="1"/>
     <col min="16" max="16" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -51091,11 +51093,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="V1:W1"/>
     <mergeCell ref="X1:Y1"/>
     <mergeCell ref="Z1:AA1"/>
     <mergeCell ref="H1:I1"/>
@@ -51103,6 +51100,11 @@
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
